--- a/data/2nd Round/Corrected/Mo_125Se_400Sb_Results Table.xlsx
+++ b/data/2nd Round/Corrected/Mo_125Se_400Sb_Results Table.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Corrected Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -507,6 +506,16 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Rseriescm2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Rshuntcm2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -547,9 +556,6 @@
       <c r="L2" t="n">
         <v>0.00013416</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>14.549</v>
       </c>
@@ -562,6 +568,12 @@
         <is>
           <t>08/21/2026</t>
         </is>
+      </c>
+      <c r="S2" t="n">
+        <v>9.339798544872131</v>
+      </c>
+      <c r="T2" t="n">
+        <v>16.78820772692493</v>
       </c>
     </row>
     <row r="3">
@@ -603,9 +615,6 @@
       <c r="L3" t="n">
         <v>0.00012503</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>14.548</v>
       </c>
@@ -618,6 +627,12 @@
         <is>
           <t>08/21/2026</t>
         </is>
+      </c>
+      <c r="S3" t="n">
+        <v>13.53124955175048</v>
+      </c>
+      <c r="T3" t="n">
+        <v>17.5778432648734</v>
       </c>
     </row>
     <row r="4">
@@ -659,9 +674,6 @@
       <c r="L4" t="n">
         <v>0.00059237</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>14.829</v>
       </c>
@@ -674,6 +686,12 @@
         <is>
           <t>08/21/2026</t>
         </is>
+      </c>
+      <c r="S4" t="n">
+        <v>13.66137319215128</v>
+      </c>
+      <c r="T4" t="n">
+        <v>56.85818708333982</v>
       </c>
     </row>
     <row r="5">
@@ -715,9 +733,6 @@
       <c r="L5" t="n">
         <v>0.00067482</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>14.57</v>
       </c>
@@ -730,6 +745,12 @@
         <is>
           <t>08/21/2026</t>
         </is>
+      </c>
+      <c r="S5" t="n">
+        <v>11.93610780313525</v>
+      </c>
+      <c r="T5" t="n">
+        <v>50.31506427934541</v>
       </c>
     </row>
     <row r="6">
@@ -771,9 +792,6 @@
       <c r="L6" t="n">
         <v>0.00056428</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>14.572</v>
       </c>
@@ -786,6 +804,12 @@
         <is>
           <t>08/21/2026</t>
         </is>
+      </c>
+      <c r="S6" t="n">
+        <v>11.55523316881463</v>
+      </c>
+      <c r="T6" t="n">
+        <v>46.44507797712011</v>
       </c>
     </row>
     <row r="7">
@@ -827,9 +851,6 @@
       <c r="L7" t="n">
         <v>0.0002483</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>14.822</v>
       </c>
@@ -842,6 +863,12 @@
         <is>
           <t>08/21/2026</t>
         </is>
+      </c>
+      <c r="S7" t="n">
+        <v>12.96255547963011</v>
+      </c>
+      <c r="T7" t="n">
+        <v>20.95727694799133</v>
       </c>
     </row>
     <row r="8">
@@ -883,9 +910,6 @@
       <c r="L8" t="n">
         <v>0.00026352</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>14.561</v>
       </c>
@@ -898,6 +922,12 @@
         <is>
           <t>08/21/2026</t>
         </is>
+      </c>
+      <c r="S8" t="n">
+        <v>14.38030555229867</v>
+      </c>
+      <c r="T8" t="n">
+        <v>21.36572376390288</v>
       </c>
     </row>
     <row r="9">
@@ -939,9 +969,6 @@
       <c r="L9" t="n">
         <v>0.00048925</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>14.573</v>
       </c>
@@ -955,7 +982,14 @@
           <t>08/21/2026</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>7.792806865660197</v>
+      </c>
+      <c r="T9" t="n">
+        <v>66.08701524137381</v>
+      </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
